--- a/artfynd/A 36808-2019 artfynd.xlsx
+++ b/artfynd/A 36808-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36808-2019 artfynd.xlsx
+++ b/artfynd/A 36808-2019 artfynd.xlsx
@@ -8290,7 +8290,7 @@
         <v>122073111</v>
       </c>
       <c r="B67" t="n">
-        <v>57374</v>
+        <v>57379</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>

--- a/artfynd/A 36808-2019 artfynd.xlsx
+++ b/artfynd/A 36808-2019 artfynd.xlsx
@@ -8305,11 +8305,6 @@
       <c r="E67" t="n">
         <v>100109</v>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>

--- a/artfynd/A 36808-2019 artfynd.xlsx
+++ b/artfynd/A 36808-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6867,14 +6867,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>79483653</v>
+        <v>79483702</v>
       </c>
       <c r="B55" t="n">
-        <v>78072</v>
+        <v>56395</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6883,34 +6883,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Norr Åviksberget, Hjd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>406491.2328189181</v>
+        <v>406651.9424989646</v>
       </c>
       <c r="R55" t="n">
-        <v>6969896.029279779</v>
+        <v>6969770.343244345</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6972,14 +6977,14 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Linda Johannesson, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>79483702</v>
+        <v>79483703</v>
       </c>
       <c r="B56" t="n">
         <v>56395</v>
@@ -7024,10 +7029,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>406651.9424989646</v>
+        <v>406650.2304488845</v>
       </c>
       <c r="R56" t="n">
-        <v>6969770.343244345</v>
+        <v>6969774.505063089</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7096,7 +7101,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>79483703</v>
+        <v>79483701</v>
       </c>
       <c r="B57" t="n">
         <v>56395</v>
@@ -7132,7 +7137,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7141,10 +7146,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>406650.2304488845</v>
+        <v>406662.4988823257</v>
       </c>
       <c r="R57" t="n">
-        <v>6969774.505063089</v>
+        <v>6969771.413607499</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7213,7 +7218,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>79483701</v>
+        <v>79483663</v>
       </c>
       <c r="B58" t="n">
         <v>56395</v>
@@ -7249,7 +7254,7 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7258,10 +7263,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>406662.4988823257</v>
+        <v>406540.5423448945</v>
       </c>
       <c r="R58" t="n">
-        <v>6969771.413607499</v>
+        <v>6969715.477706877</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7330,7 +7335,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>79483663</v>
+        <v>79483661</v>
       </c>
       <c r="B59" t="n">
         <v>56395</v>
@@ -7375,10 +7380,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>406540.5423448945</v>
+        <v>406543.7027316461</v>
       </c>
       <c r="R59" t="n">
-        <v>6969715.477706877</v>
+        <v>6969730.012033386</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7447,7 +7452,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>79483661</v>
+        <v>79105368</v>
       </c>
       <c r="B60" t="n">
         <v>56395</v>
@@ -7481,21 +7486,16 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Norr Åviksberget, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>406543.7027316461</v>
+        <v>406833.9884686128</v>
       </c>
       <c r="R60" t="n">
-        <v>6969730.012033386</v>
+        <v>6969638.113208781</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7540,6 +7540,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7552,19 +7557,23 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>79105368</v>
+        <v>79105419</v>
       </c>
       <c r="B61" t="n">
         <v>56395</v>
@@ -7604,10 +7613,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>406833.9884686128</v>
+        <v>406697.2327805863</v>
       </c>
       <c r="R61" t="n">
-        <v>6969638.113208781</v>
+        <v>6969721.524594567</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7685,7 +7694,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>79483664</v>
+        <v>79105434</v>
       </c>
       <c r="B62" t="n">
         <v>56395</v>
@@ -7719,21 +7728,16 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Norr Åviksberget, Hjd</t>
+          <t>N om Åviksberget, Västra, Hjd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>406539.6017320502</v>
+        <v>406547.1787033188</v>
       </c>
       <c r="R62" t="n">
-        <v>6969714.590499355</v>
+        <v>6969723.514730502</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7778,6 +7782,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>spår</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7790,26 +7799,30 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Martin Westberg</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Ingemar Södergren</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>79105419</v>
+        <v>81987619</v>
       </c>
       <c r="B63" t="n">
-        <v>56395</v>
+        <v>57435</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7818,16 +7831,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>100077</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7835,17 +7848,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>N om Åviksberget, Västra, Hjd</t>
+          <t>södra bäcken, Beten, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>406697.2327805863</v>
+        <v>406429.4000986402</v>
       </c>
       <c r="R63" t="n">
-        <v>6969721.524594567</v>
+        <v>6969653.752070095</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7872,7 +7897,7 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
@@ -7882,17 +7907,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7907,30 +7927,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Kent Moén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
+          <t>Kent Moén, Eva Moén</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>79105434</v>
+        <v>122073111</v>
       </c>
       <c r="B64" t="n">
-        <v>56395</v>
+        <v>57379</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7941,11 +7957,6 @@
       <c r="E64" t="n">
         <v>100109</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>Picoides tridactylus</t>
@@ -7956,17 +7967,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>N om Åviksberget, Västra, Hjd</t>
+          <t>Storsjö, Beten, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>406547.1787033188</v>
+        <v>406778</v>
       </c>
       <c r="R64" t="n">
-        <v>6969723.514730502</v>
+        <v>6969971</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7993,27 +8018,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2019-07-24</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>spår</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8028,383 +8048,15 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Martin Westberg</t>
+          <t>Kent Moén</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Martin Westberg, Ingemar Södergren, Monika Norberg, Maria Danvind, Barbro Strååt</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2019 Jämtlands län</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>81987619</v>
-      </c>
-      <c r="B65" t="n">
-        <v>57435</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>100077</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Utter</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Lutra lutra</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>södra bäcken, Beten, Storsjö, Hjd</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>406429.4000986402</v>
-      </c>
-      <c r="R65" t="n">
-        <v>6969653.752070095</v>
-      </c>
-      <c r="S65" t="n">
-        <v>10</v>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>2020-02-01</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA65" t="inlineStr">
-        <is>
-          <t>2020-02-01</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG65" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT65" t="inlineStr"/>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>Kent Moén</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
-        <is>
           <t>Kent Moén, Eva Moén</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>113446833</v>
-      </c>
-      <c r="B66" t="n">
-        <v>56115</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>100077</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Utter</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Lutra lutra</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>södra bäcken, Beten, Storsjö, Hjd</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>406429</v>
-      </c>
-      <c r="R66" t="n">
-        <v>6969654</v>
-      </c>
-      <c r="S66" t="n">
-        <v>10</v>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y66" t="inlineStr">
-        <is>
-          <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AA66" t="inlineStr">
-        <is>
-          <t>2023-11-29</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Spår uppströms mot västra rotsjön. Födosökande.</t>
-        </is>
-      </c>
-      <c r="AD66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT66" t="inlineStr"/>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>Kent Moén</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>Kent Moén</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>122073111</v>
-      </c>
-      <c r="B67" t="n">
-        <v>57379</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>100109</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Storsjö, Beten, Storsjö, Hjd</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>406778</v>
-      </c>
-      <c r="R67" t="n">
-        <v>6969971</v>
-      </c>
-      <c r="S67" t="n">
-        <v>10</v>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2025-01-12</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>2025-01-12</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AD67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT67" t="inlineStr"/>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>Kent Moén</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>Kent Moén, Eva Moén</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
